--- a/data/members.xlsx
+++ b/data/members.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/06c0feee4e58a39d/Desktop/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="4" documentId="8_{4C366B8F-9A87-4F80-B4D3-6861D497F238}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{37FDBF12-CEAC-4FBA-B73F-CA305C66AA6D}"/>
+  <xr:revisionPtr revIDLastSave="5" documentId="8_{4C366B8F-9A87-4F80-B4D3-6861D497F238}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C5539E21-BA6D-445C-A224-E5C3508B4771}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{E1BBCC77-337F-4DF8-A50E-16E665B8EEBD}"/>
   </bookViews>
@@ -45,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4968" uniqueCount="1997">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4664" uniqueCount="1996">
   <si>
     <t>CP, 염석대, NSU, YB, 늪지대, 정선대, JSA</t>
   </si>
@@ -6035,9 +6035,6 @@
   </si>
   <si>
     <t>뽀인구단, BGM</t>
-  </si>
-  <si>
-    <t>null</t>
   </si>
   <si>
     <t>수정일</t>
@@ -6427,6 +6424,10 @@
 </externalLink>
 </file>
 
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 테마">
   <a:themeElements>
@@ -6776,7 +6777,7 @@
         <v>664</v>
       </c>
       <c r="J1" s="2" t="s">
-        <v>1996</v>
+        <v>1995</v>
       </c>
       <c r="K1" s="2" t="s">
         <v>665</v>
@@ -16884,9 +16885,7 @@
       <c r="F203" s="9" t="s">
         <v>53</v>
       </c>
-      <c r="G203" s="9" t="s">
-        <v>1995</v>
-      </c>
+      <c r="G203" s="9"/>
       <c r="H203" s="9" t="s">
         <v>1157</v>
       </c>
@@ -17419,18 +17418,14 @@
       <c r="C214" s="13">
         <v>6372</v>
       </c>
-      <c r="D214" s="14" t="s">
-        <v>1995</v>
-      </c>
+      <c r="D214" s="14"/>
       <c r="E214" s="13" t="s">
         <v>47</v>
       </c>
       <c r="F214" s="13" t="s">
         <v>48</v>
       </c>
-      <c r="G214" s="13" t="s">
-        <v>1995</v>
-      </c>
+      <c r="G214" s="13"/>
       <c r="H214" s="13" t="s">
         <v>1188</v>
       </c>
@@ -22331,9 +22326,7 @@
       <c r="C318" s="17">
         <v>68</v>
       </c>
-      <c r="D318" s="14" t="s">
-        <v>1995</v>
-      </c>
+      <c r="D318" s="14"/>
       <c r="E318" s="13" t="s">
         <v>47</v>
       </c>
@@ -22415,9 +22408,7 @@
       <c r="C320" s="13">
         <v>96</v>
       </c>
-      <c r="D320" s="14" t="s">
-        <v>1995</v>
-      </c>
+      <c r="D320" s="14"/>
       <c r="E320" s="13" t="s">
         <v>47</v>
       </c>
@@ -22499,9 +22490,7 @@
       <c r="C322" s="13">
         <v>171</v>
       </c>
-      <c r="D322" s="14" t="s">
-        <v>1995</v>
-      </c>
+      <c r="D322" s="14"/>
       <c r="E322" s="13" t="s">
         <v>47</v>
       </c>
@@ -22625,9 +22614,7 @@
       <c r="C325" s="9">
         <v>107</v>
       </c>
-      <c r="D325" s="10" t="s">
-        <v>1995</v>
-      </c>
+      <c r="D325" s="10"/>
       <c r="E325" s="9" t="s">
         <v>47</v>
       </c>
@@ -22709,9 +22696,7 @@
       <c r="C327" s="9">
         <v>163</v>
       </c>
-      <c r="D327" s="10" t="s">
-        <v>1995</v>
-      </c>
+      <c r="D327" s="10"/>
       <c r="E327" s="9" t="s">
         <v>47</v>
       </c>
@@ -22793,9 +22778,7 @@
       <c r="C329" s="9">
         <v>159</v>
       </c>
-      <c r="D329" s="10" t="s">
-        <v>1995</v>
-      </c>
+      <c r="D329" s="10"/>
       <c r="E329" s="9" t="s">
         <v>47</v>
       </c>
@@ -22877,9 +22860,7 @@
       <c r="C331" s="19">
         <v>161</v>
       </c>
-      <c r="D331" s="10" t="s">
-        <v>1995</v>
-      </c>
+      <c r="D331" s="10"/>
       <c r="E331" s="9" t="s">
         <v>47</v>
       </c>
@@ -22919,9 +22900,7 @@
       <c r="C332" s="17">
         <v>121</v>
       </c>
-      <c r="D332" s="14" t="s">
-        <v>1995</v>
-      </c>
+      <c r="D332" s="14"/>
       <c r="E332" s="13" t="s">
         <v>47</v>
       </c>
@@ -22961,9 +22940,7 @@
       <c r="C333" s="9">
         <v>128</v>
       </c>
-      <c r="D333" s="10" t="s">
-        <v>1995</v>
-      </c>
+      <c r="D333" s="10"/>
       <c r="E333" s="9" t="s">
         <v>47</v>
       </c>
@@ -23003,9 +22980,7 @@
       <c r="C334" s="13">
         <v>133</v>
       </c>
-      <c r="D334" s="14" t="s">
-        <v>1995</v>
-      </c>
+      <c r="D334" s="14"/>
       <c r="E334" s="13" t="s">
         <v>47</v>
       </c>
@@ -23087,9 +23062,7 @@
       <c r="C336" s="17">
         <v>139</v>
       </c>
-      <c r="D336" s="14" t="s">
-        <v>1995</v>
-      </c>
+      <c r="D336" s="14"/>
       <c r="E336" s="13" t="s">
         <v>47</v>
       </c>
@@ -23297,9 +23270,7 @@
       <c r="C341" s="9">
         <v>6255</v>
       </c>
-      <c r="D341" s="10" t="s">
-        <v>1995</v>
-      </c>
+      <c r="D341" s="10"/>
       <c r="E341" s="9" t="s">
         <v>47</v>
       </c>
@@ -23385,9 +23356,7 @@
       <c r="C343" s="19">
         <v>6230</v>
       </c>
-      <c r="D343" s="10" t="s">
-        <v>1995</v>
-      </c>
+      <c r="D343" s="10"/>
       <c r="E343" s="9" t="s">
         <v>47</v>
       </c>
@@ -24057,9 +24026,7 @@
       <c r="C359" s="9">
         <v>6233</v>
       </c>
-      <c r="D359" s="10" t="s">
-        <v>1995</v>
-      </c>
+      <c r="D359" s="10"/>
       <c r="E359" s="9" t="s">
         <v>47</v>
       </c>
@@ -24099,9 +24066,7 @@
       <c r="C360" s="13">
         <v>6323</v>
       </c>
-      <c r="D360" s="14" t="s">
-        <v>1995</v>
-      </c>
+      <c r="D360" s="14"/>
       <c r="E360" s="13" t="s">
         <v>47</v>
       </c>
@@ -24225,9 +24190,7 @@
       <c r="C363" s="9">
         <v>6319</v>
       </c>
-      <c r="D363" s="10" t="s">
-        <v>1995</v>
-      </c>
+      <c r="D363" s="10"/>
       <c r="E363" s="9" t="s">
         <v>47</v>
       </c>
@@ -24309,9 +24272,7 @@
       <c r="C365" s="9">
         <v>6395</v>
       </c>
-      <c r="D365" s="10" t="s">
-        <v>1995</v>
-      </c>
+      <c r="D365" s="10"/>
       <c r="E365" s="9" t="s">
         <v>47</v>
       </c>
@@ -24435,9 +24396,7 @@
       <c r="C368" s="13">
         <v>6329</v>
       </c>
-      <c r="D368" s="14" t="s">
-        <v>1995</v>
-      </c>
+      <c r="D368" s="14"/>
       <c r="E368" s="13" t="s">
         <v>47</v>
       </c>
@@ -24519,9 +24478,7 @@
       <c r="C370" s="17">
         <v>6258</v>
       </c>
-      <c r="D370" s="14" t="s">
-        <v>1995</v>
-      </c>
+      <c r="D370" s="14"/>
       <c r="E370" s="13" t="s">
         <v>47</v>
       </c>
@@ -24687,9 +24644,7 @@
       <c r="C374" s="13">
         <v>6291</v>
       </c>
-      <c r="D374" s="14" t="s">
-        <v>1995</v>
-      </c>
+      <c r="D374" s="14"/>
       <c r="E374" s="13" t="s">
         <v>47</v>
       </c>
@@ -24771,9 +24726,7 @@
       <c r="C376" s="13">
         <v>6238</v>
       </c>
-      <c r="D376" s="14" t="s">
-        <v>1995</v>
-      </c>
+      <c r="D376" s="14"/>
       <c r="E376" s="13" t="s">
         <v>47</v>
       </c>
@@ -24813,9 +24766,7 @@
       <c r="C377" s="9">
         <v>6376</v>
       </c>
-      <c r="D377" s="10" t="s">
-        <v>1995</v>
-      </c>
+      <c r="D377" s="10"/>
       <c r="E377" s="9" t="s">
         <v>47</v>
       </c>
@@ -25275,9 +25226,7 @@
       <c r="C388" s="13">
         <v>6307</v>
       </c>
-      <c r="D388" s="14" t="s">
-        <v>1995</v>
-      </c>
+      <c r="D388" s="14"/>
       <c r="E388" s="13" t="s">
         <v>47</v>
       </c>
@@ -25317,9 +25266,7 @@
       <c r="C389" s="19">
         <v>6404</v>
       </c>
-      <c r="D389" s="10" t="s">
-        <v>1995</v>
-      </c>
+      <c r="D389" s="10"/>
       <c r="E389" s="9" t="s">
         <v>47</v>
       </c>
@@ -25359,9 +25306,7 @@
       <c r="C390" s="13">
         <v>6248</v>
       </c>
-      <c r="D390" s="14" t="s">
-        <v>1995</v>
-      </c>
+      <c r="D390" s="14"/>
       <c r="E390" s="13" t="s">
         <v>47</v>
       </c>
@@ -25485,9 +25430,7 @@
       <c r="C393" s="19">
         <v>6396</v>
       </c>
-      <c r="D393" s="10" t="s">
-        <v>1995</v>
-      </c>
+      <c r="D393" s="10"/>
       <c r="E393" s="9" t="s">
         <v>47</v>
       </c>
@@ -25569,9 +25512,7 @@
       <c r="C395" s="19">
         <v>6407</v>
       </c>
-      <c r="D395" s="10" t="s">
-        <v>1995</v>
-      </c>
+      <c r="D395" s="10"/>
       <c r="E395" s="9" t="s">
         <v>47</v>
       </c>
@@ -26287,18 +26228,14 @@
       <c r="C412" s="17">
         <v>168</v>
       </c>
-      <c r="D412" s="14" t="s">
-        <v>1995</v>
-      </c>
+      <c r="D412" s="14"/>
       <c r="E412" s="13" t="s">
         <v>47</v>
       </c>
       <c r="F412" s="13" t="s">
         <v>48</v>
       </c>
-      <c r="G412" s="13" t="s">
-        <v>1995</v>
-      </c>
+      <c r="G412" s="13"/>
       <c r="H412" s="13" t="s">
         <v>50</v>
       </c>
@@ -26329,18 +26266,14 @@
       <c r="C413" s="19">
         <v>123</v>
       </c>
-      <c r="D413" s="10" t="s">
-        <v>1995</v>
-      </c>
+      <c r="D413" s="10"/>
       <c r="E413" s="9" t="s">
         <v>47</v>
       </c>
       <c r="F413" s="9" t="s">
         <v>48</v>
       </c>
-      <c r="G413" s="9" t="s">
-        <v>1995</v>
-      </c>
+      <c r="G413" s="9"/>
       <c r="H413" s="9" t="s">
         <v>50</v>
       </c>
@@ -26380,9 +26313,7 @@
       <c r="F414" s="13" t="s">
         <v>48</v>
       </c>
-      <c r="G414" s="13" t="s">
-        <v>1995</v>
-      </c>
+      <c r="G414" s="13"/>
       <c r="H414" s="13" t="s">
         <v>50</v>
       </c>
@@ -26413,18 +26344,14 @@
       <c r="C415" s="9">
         <v>6410</v>
       </c>
-      <c r="D415" s="10" t="s">
-        <v>1995</v>
-      </c>
+      <c r="D415" s="10"/>
       <c r="E415" s="9" t="s">
         <v>47</v>
       </c>
       <c r="F415" s="9" t="s">
         <v>48</v>
       </c>
-      <c r="G415" s="9" t="s">
-        <v>1995</v>
-      </c>
+      <c r="G415" s="9"/>
       <c r="H415" s="9" t="s">
         <v>50</v>
       </c>
@@ -26455,18 +26382,14 @@
       <c r="C416" s="13">
         <v>95</v>
       </c>
-      <c r="D416" s="14" t="s">
-        <v>1995</v>
-      </c>
+      <c r="D416" s="14"/>
       <c r="E416" s="13" t="s">
         <v>47</v>
       </c>
       <c r="F416" s="13" t="s">
         <v>48</v>
       </c>
-      <c r="G416" s="13" t="s">
-        <v>1995</v>
-      </c>
+      <c r="G416" s="13"/>
       <c r="H416" s="13" t="s">
         <v>50</v>
       </c>
@@ -26497,18 +26420,14 @@
       <c r="C417" s="9">
         <v>6374</v>
       </c>
-      <c r="D417" s="10" t="s">
-        <v>1995</v>
-      </c>
+      <c r="D417" s="10"/>
       <c r="E417" s="9" t="s">
         <v>47</v>
       </c>
       <c r="F417" s="9" t="s">
         <v>48</v>
       </c>
-      <c r="G417" s="9" t="s">
-        <v>1995</v>
-      </c>
+      <c r="G417" s="9"/>
       <c r="H417" s="9" t="s">
         <v>50</v>
       </c>
@@ -26539,18 +26458,14 @@
       <c r="C418" s="13">
         <v>6135</v>
       </c>
-      <c r="D418" s="14" t="s">
-        <v>1995</v>
-      </c>
+      <c r="D418" s="14"/>
       <c r="E418" s="13" t="s">
         <v>47</v>
       </c>
       <c r="F418" s="13" t="s">
         <v>48</v>
       </c>
-      <c r="G418" s="13" t="s">
-        <v>1995</v>
-      </c>
+      <c r="G418" s="13"/>
       <c r="H418" s="13" t="s">
         <v>50</v>
       </c>
@@ -26581,18 +26496,14 @@
       <c r="C419" s="9">
         <v>6118</v>
       </c>
-      <c r="D419" s="10" t="s">
-        <v>1995</v>
-      </c>
+      <c r="D419" s="10"/>
       <c r="E419" s="9" t="s">
         <v>47</v>
       </c>
       <c r="F419" s="9" t="s">
         <v>48</v>
       </c>
-      <c r="G419" s="9" t="s">
-        <v>1995</v>
-      </c>
+      <c r="G419" s="9"/>
       <c r="H419" s="9" t="s">
         <v>50</v>
       </c>
@@ -26623,18 +26534,14 @@
       <c r="C420" s="13">
         <v>6327</v>
       </c>
-      <c r="D420" s="14" t="s">
-        <v>1995</v>
-      </c>
+      <c r="D420" s="14"/>
       <c r="E420" s="13" t="s">
         <v>47</v>
       </c>
       <c r="F420" s="13" t="s">
         <v>48</v>
       </c>
-      <c r="G420" s="13" t="s">
-        <v>1995</v>
-      </c>
+      <c r="G420" s="13"/>
       <c r="H420" s="13" t="s">
         <v>50</v>
       </c>
@@ -26665,18 +26572,14 @@
       <c r="C421" s="9">
         <v>6280</v>
       </c>
-      <c r="D421" s="10" t="s">
-        <v>1995</v>
-      </c>
+      <c r="D421" s="10"/>
       <c r="E421" s="9" t="s">
         <v>47</v>
       </c>
       <c r="F421" s="9" t="s">
         <v>48</v>
       </c>
-      <c r="G421" s="9" t="s">
-        <v>1995</v>
-      </c>
+      <c r="G421" s="9"/>
       <c r="H421" s="9" t="s">
         <v>50</v>
       </c>
@@ -26707,18 +26610,14 @@
       <c r="C422" s="13">
         <v>6269</v>
       </c>
-      <c r="D422" s="14" t="s">
-        <v>1995</v>
-      </c>
+      <c r="D422" s="14"/>
       <c r="E422" s="13" t="s">
         <v>47</v>
       </c>
       <c r="F422" s="13" t="s">
         <v>48</v>
       </c>
-      <c r="G422" s="13" t="s">
-        <v>1995</v>
-      </c>
+      <c r="G422" s="13"/>
       <c r="H422" s="13" t="s">
         <v>50</v>
       </c>
@@ -26749,18 +26648,14 @@
       <c r="C423" s="9">
         <v>6282</v>
       </c>
-      <c r="D423" s="10" t="s">
-        <v>1995</v>
-      </c>
+      <c r="D423" s="10"/>
       <c r="E423" s="9" t="s">
         <v>47</v>
       </c>
       <c r="F423" s="9" t="s">
         <v>48</v>
       </c>
-      <c r="G423" s="9" t="s">
-        <v>1995</v>
-      </c>
+      <c r="G423" s="9"/>
       <c r="H423" s="9" t="s">
         <v>50</v>
       </c>
@@ -26791,18 +26686,14 @@
       <c r="C424" s="13">
         <v>6165</v>
       </c>
-      <c r="D424" s="14" t="s">
-        <v>1995</v>
-      </c>
+      <c r="D424" s="14"/>
       <c r="E424" s="13" t="s">
         <v>47</v>
       </c>
       <c r="F424" s="13" t="s">
         <v>48</v>
       </c>
-      <c r="G424" s="13" t="s">
-        <v>1995</v>
-      </c>
+      <c r="G424" s="13"/>
       <c r="H424" s="13" t="s">
         <v>50</v>
       </c>
@@ -26833,18 +26724,14 @@
       <c r="C425" s="9">
         <v>6223</v>
       </c>
-      <c r="D425" s="10" t="s">
-        <v>1995</v>
-      </c>
+      <c r="D425" s="10"/>
       <c r="E425" s="9" t="s">
         <v>47</v>
       </c>
       <c r="F425" s="9" t="s">
         <v>48</v>
       </c>
-      <c r="G425" s="9" t="s">
-        <v>1995</v>
-      </c>
+      <c r="G425" s="9"/>
       <c r="H425" s="9" t="s">
         <v>50</v>
       </c>
@@ -26875,18 +26762,14 @@
       <c r="C426" s="13">
         <v>6265</v>
       </c>
-      <c r="D426" s="14" t="s">
-        <v>1995</v>
-      </c>
+      <c r="D426" s="14"/>
       <c r="E426" s="13" t="s">
         <v>47</v>
       </c>
       <c r="F426" s="13" t="s">
         <v>48</v>
       </c>
-      <c r="G426" s="13" t="s">
-        <v>1995</v>
-      </c>
+      <c r="G426" s="13"/>
       <c r="H426" s="13" t="s">
         <v>50</v>
       </c>
@@ -26917,18 +26800,14 @@
       <c r="C427" s="9">
         <v>6419</v>
       </c>
-      <c r="D427" s="10" t="s">
-        <v>1995</v>
-      </c>
+      <c r="D427" s="10"/>
       <c r="E427" s="9" t="s">
         <v>47</v>
       </c>
       <c r="F427" s="9" t="s">
         <v>48</v>
       </c>
-      <c r="G427" s="9" t="s">
-        <v>1995</v>
-      </c>
+      <c r="G427" s="9"/>
       <c r="H427" s="9" t="s">
         <v>50</v>
       </c>
@@ -26959,18 +26838,14 @@
       <c r="C428" s="13">
         <v>6450</v>
       </c>
-      <c r="D428" s="14" t="s">
-        <v>1995</v>
-      </c>
+      <c r="D428" s="14"/>
       <c r="E428" s="13" t="s">
         <v>47</v>
       </c>
       <c r="F428" s="13" t="s">
         <v>48</v>
       </c>
-      <c r="G428" s="13" t="s">
-        <v>1995</v>
-      </c>
+      <c r="G428" s="13"/>
       <c r="H428" s="13" t="s">
         <v>50</v>
       </c>
@@ -27001,18 +26876,14 @@
       <c r="C429" s="9">
         <v>111</v>
       </c>
-      <c r="D429" s="10" t="s">
-        <v>1995</v>
-      </c>
+      <c r="D429" s="10"/>
       <c r="E429" s="9" t="s">
         <v>47</v>
       </c>
       <c r="F429" s="9" t="s">
         <v>48</v>
       </c>
-      <c r="G429" s="9" t="s">
-        <v>1995</v>
-      </c>
+      <c r="G429" s="9"/>
       <c r="H429" s="9" t="s">
         <v>50</v>
       </c>
@@ -27043,18 +26914,14 @@
       <c r="C430" s="13">
         <v>114</v>
       </c>
-      <c r="D430" s="14" t="s">
-        <v>1995</v>
-      </c>
+      <c r="D430" s="14"/>
       <c r="E430" s="13" t="s">
         <v>47</v>
       </c>
       <c r="F430" s="13" t="s">
         <v>48</v>
       </c>
-      <c r="G430" s="13" t="s">
-        <v>1995</v>
-      </c>
+      <c r="G430" s="13"/>
       <c r="H430" s="13" t="s">
         <v>50</v>
       </c>
@@ -27085,18 +26952,14 @@
       <c r="C431" s="9">
         <v>6464</v>
       </c>
-      <c r="D431" s="10" t="s">
-        <v>1995</v>
-      </c>
+      <c r="D431" s="10"/>
       <c r="E431" s="9" t="s">
         <v>47</v>
       </c>
       <c r="F431" s="9" t="s">
         <v>53</v>
       </c>
-      <c r="G431" s="9" t="s">
-        <v>1995</v>
-      </c>
+      <c r="G431" s="9"/>
       <c r="H431" s="9" t="s">
         <v>50</v>
       </c>
@@ -27127,18 +26990,14 @@
       <c r="C432" s="17">
         <v>6146</v>
       </c>
-      <c r="D432" s="14" t="s">
-        <v>1995</v>
-      </c>
+      <c r="D432" s="14"/>
       <c r="E432" s="13" t="s">
         <v>47</v>
       </c>
       <c r="F432" s="13" t="s">
         <v>53</v>
       </c>
-      <c r="G432" s="13" t="s">
-        <v>1995</v>
-      </c>
+      <c r="G432" s="13"/>
       <c r="H432" s="13" t="s">
         <v>50</v>
       </c>
@@ -27169,18 +27028,14 @@
       <c r="C433" s="19">
         <v>143</v>
       </c>
-      <c r="D433" s="10" t="s">
-        <v>1995</v>
-      </c>
+      <c r="D433" s="10"/>
       <c r="E433" s="9" t="s">
         <v>47</v>
       </c>
       <c r="F433" s="9" t="s">
         <v>53</v>
       </c>
-      <c r="G433" s="9" t="s">
-        <v>1995</v>
-      </c>
+      <c r="G433" s="9"/>
       <c r="H433" s="9" t="s">
         <v>50</v>
       </c>
@@ -27220,9 +27075,7 @@
       <c r="F434" s="13" t="s">
         <v>53</v>
       </c>
-      <c r="G434" s="13" t="s">
-        <v>1995</v>
-      </c>
+      <c r="G434" s="13"/>
       <c r="H434" s="13" t="s">
         <v>50</v>
       </c>
@@ -27253,18 +27106,14 @@
       <c r="C435" s="9">
         <v>116</v>
       </c>
-      <c r="D435" s="10" t="s">
-        <v>1995</v>
-      </c>
+      <c r="D435" s="10"/>
       <c r="E435" s="9" t="s">
         <v>47</v>
       </c>
       <c r="F435" s="9" t="s">
         <v>53</v>
       </c>
-      <c r="G435" s="9" t="s">
-        <v>1995</v>
-      </c>
+      <c r="G435" s="9"/>
       <c r="H435" s="9" t="s">
         <v>50</v>
       </c>
@@ -27295,18 +27144,14 @@
       <c r="C436" s="13">
         <v>6209</v>
       </c>
-      <c r="D436" s="14" t="s">
-        <v>1995</v>
-      </c>
+      <c r="D436" s="14"/>
       <c r="E436" s="13" t="s">
         <v>47</v>
       </c>
       <c r="F436" s="13" t="s">
         <v>53</v>
       </c>
-      <c r="G436" s="13" t="s">
-        <v>1995</v>
-      </c>
+      <c r="G436" s="13"/>
       <c r="H436" s="13" t="s">
         <v>50</v>
       </c>
@@ -27337,18 +27182,14 @@
       <c r="C437" s="9">
         <v>6340</v>
       </c>
-      <c r="D437" s="10" t="s">
-        <v>1995</v>
-      </c>
+      <c r="D437" s="10"/>
       <c r="E437" s="9" t="s">
         <v>47</v>
       </c>
       <c r="F437" s="9" t="s">
         <v>53</v>
       </c>
-      <c r="G437" s="9" t="s">
-        <v>1995</v>
-      </c>
+      <c r="G437" s="9"/>
       <c r="H437" s="9" t="s">
         <v>50</v>
       </c>
@@ -27379,18 +27220,14 @@
       <c r="C438" s="13">
         <v>6120</v>
       </c>
-      <c r="D438" s="14" t="s">
-        <v>1995</v>
-      </c>
+      <c r="D438" s="14"/>
       <c r="E438" s="13" t="s">
         <v>47</v>
       </c>
       <c r="F438" s="13" t="s">
         <v>53</v>
       </c>
-      <c r="G438" s="13" t="s">
-        <v>1995</v>
-      </c>
+      <c r="G438" s="13"/>
       <c r="H438" s="13" t="s">
         <v>50</v>
       </c>
@@ -27421,18 +27258,14 @@
       <c r="C439" s="9">
         <v>6202</v>
       </c>
-      <c r="D439" s="10" t="s">
-        <v>1995</v>
-      </c>
+      <c r="D439" s="10"/>
       <c r="E439" s="9" t="s">
         <v>47</v>
       </c>
       <c r="F439" s="9" t="s">
         <v>53</v>
       </c>
-      <c r="G439" s="9" t="s">
-        <v>1995</v>
-      </c>
+      <c r="G439" s="9"/>
       <c r="H439" s="9" t="s">
         <v>50</v>
       </c>
@@ -27463,18 +27296,14 @@
       <c r="C440" s="13">
         <v>6166</v>
       </c>
-      <c r="D440" s="14" t="s">
-        <v>1995</v>
-      </c>
+      <c r="D440" s="14"/>
       <c r="E440" s="13" t="s">
         <v>47</v>
       </c>
       <c r="F440" s="13" t="s">
         <v>53</v>
       </c>
-      <c r="G440" s="13" t="s">
-        <v>1995</v>
-      </c>
+      <c r="G440" s="13"/>
       <c r="H440" s="13" t="s">
         <v>50</v>
       </c>
@@ -27505,18 +27334,14 @@
       <c r="C441" s="9">
         <v>6305</v>
       </c>
-      <c r="D441" s="10" t="s">
-        <v>1995</v>
-      </c>
+      <c r="D441" s="10"/>
       <c r="E441" s="9" t="s">
         <v>47</v>
       </c>
       <c r="F441" s="9" t="s">
         <v>53</v>
       </c>
-      <c r="G441" s="9" t="s">
-        <v>1995</v>
-      </c>
+      <c r="G441" s="9"/>
       <c r="H441" s="9" t="s">
         <v>50</v>
       </c>
@@ -27547,18 +27372,14 @@
       <c r="C442" s="13">
         <v>6350</v>
       </c>
-      <c r="D442" s="14" t="s">
-        <v>1995</v>
-      </c>
+      <c r="D442" s="14"/>
       <c r="E442" s="13" t="s">
         <v>47</v>
       </c>
       <c r="F442" s="13" t="s">
         <v>53</v>
       </c>
-      <c r="G442" s="13" t="s">
-        <v>1995</v>
-      </c>
+      <c r="G442" s="13"/>
       <c r="H442" s="13" t="s">
         <v>50</v>
       </c>
@@ -27589,18 +27410,14 @@
       <c r="C443" s="9">
         <v>6227</v>
       </c>
-      <c r="D443" s="10" t="s">
-        <v>1995</v>
-      </c>
+      <c r="D443" s="10"/>
       <c r="E443" s="9" t="s">
         <v>47</v>
       </c>
       <c r="F443" s="9" t="s">
         <v>53</v>
       </c>
-      <c r="G443" s="9" t="s">
-        <v>1995</v>
-      </c>
+      <c r="G443" s="9"/>
       <c r="H443" s="9" t="s">
         <v>50</v>
       </c>
@@ -27631,18 +27448,14 @@
       <c r="C444" s="13">
         <v>6328</v>
       </c>
-      <c r="D444" s="14" t="s">
-        <v>1995</v>
-      </c>
+      <c r="D444" s="14"/>
       <c r="E444" s="13" t="s">
         <v>47</v>
       </c>
       <c r="F444" s="13" t="s">
         <v>53</v>
       </c>
-      <c r="G444" s="13" t="s">
-        <v>1995</v>
-      </c>
+      <c r="G444" s="13"/>
       <c r="H444" s="13" t="s">
         <v>50</v>
       </c>
@@ -27673,18 +27486,14 @@
       <c r="C445" s="9">
         <v>6173</v>
       </c>
-      <c r="D445" s="10" t="s">
-        <v>1995</v>
-      </c>
+      <c r="D445" s="10"/>
       <c r="E445" s="9" t="s">
         <v>47</v>
       </c>
       <c r="F445" s="9" t="s">
         <v>53</v>
       </c>
-      <c r="G445" s="9" t="s">
-        <v>1995</v>
-      </c>
+      <c r="G445" s="9"/>
       <c r="H445" s="9" t="s">
         <v>50</v>
       </c>
@@ -27715,18 +27524,14 @@
       <c r="C446" s="13">
         <v>6390</v>
       </c>
-      <c r="D446" s="14" t="s">
-        <v>1995</v>
-      </c>
+      <c r="D446" s="14"/>
       <c r="E446" s="13" t="s">
         <v>47</v>
       </c>
       <c r="F446" s="13" t="s">
         <v>53</v>
       </c>
-      <c r="G446" s="13" t="s">
-        <v>1995</v>
-      </c>
+      <c r="G446" s="13"/>
       <c r="H446" s="13" t="s">
         <v>50</v>
       </c>
@@ -27757,18 +27562,14 @@
       <c r="C447" s="9">
         <v>6378</v>
       </c>
-      <c r="D447" s="10" t="s">
-        <v>1995</v>
-      </c>
+      <c r="D447" s="10"/>
       <c r="E447" s="9" t="s">
         <v>47</v>
       </c>
       <c r="F447" s="9" t="s">
         <v>53</v>
       </c>
-      <c r="G447" s="9" t="s">
-        <v>1995</v>
-      </c>
+      <c r="G447" s="9"/>
       <c r="H447" s="9" t="s">
         <v>50</v>
       </c>
@@ -27799,18 +27600,14 @@
       <c r="C448" s="13">
         <v>6242</v>
       </c>
-      <c r="D448" s="14" t="s">
-        <v>1995</v>
-      </c>
+      <c r="D448" s="14"/>
       <c r="E448" s="13" t="s">
         <v>47</v>
       </c>
       <c r="F448" s="13" t="s">
         <v>53</v>
       </c>
-      <c r="G448" s="13" t="s">
-        <v>1995</v>
-      </c>
+      <c r="G448" s="13"/>
       <c r="H448" s="13" t="s">
         <v>50</v>
       </c>
@@ -27850,9 +27647,7 @@
       <c r="F449" s="9" t="s">
         <v>58</v>
       </c>
-      <c r="G449" s="9" t="s">
-        <v>1995</v>
-      </c>
+      <c r="G449" s="9"/>
       <c r="H449" s="9" t="s">
         <v>50</v>
       </c>
@@ -27890,9 +27685,7 @@
       <c r="F450" s="13" t="s">
         <v>58</v>
       </c>
-      <c r="G450" s="13" t="s">
-        <v>1995</v>
-      </c>
+      <c r="G450" s="13"/>
       <c r="H450" s="13" t="s">
         <v>50</v>
       </c>
@@ -27923,18 +27716,14 @@
       <c r="C451" s="19">
         <v>158</v>
       </c>
-      <c r="D451" s="10" t="s">
-        <v>1995</v>
-      </c>
+      <c r="D451" s="10"/>
       <c r="E451" s="9" t="s">
         <v>47</v>
       </c>
       <c r="F451" s="9" t="s">
         <v>58</v>
       </c>
-      <c r="G451" s="9" t="s">
-        <v>1995</v>
-      </c>
+      <c r="G451" s="9"/>
       <c r="H451" s="9" t="s">
         <v>50</v>
       </c>
@@ -27965,18 +27754,14 @@
       <c r="C452" s="17">
         <v>106</v>
       </c>
-      <c r="D452" s="14" t="s">
-        <v>1995</v>
-      </c>
+      <c r="D452" s="14"/>
       <c r="E452" s="13" t="s">
         <v>47</v>
       </c>
       <c r="F452" s="13" t="s">
         <v>58</v>
       </c>
-      <c r="G452" s="13" t="s">
-        <v>1995</v>
-      </c>
+      <c r="G452" s="13"/>
       <c r="H452" s="13" t="s">
         <v>50</v>
       </c>
@@ -28007,18 +27792,14 @@
       <c r="C453" s="19">
         <v>160</v>
       </c>
-      <c r="D453" s="10" t="s">
-        <v>1995</v>
-      </c>
+      <c r="D453" s="10"/>
       <c r="E453" s="9" t="s">
         <v>47</v>
       </c>
       <c r="F453" s="9" t="s">
         <v>58</v>
       </c>
-      <c r="G453" s="9" t="s">
-        <v>1995</v>
-      </c>
+      <c r="G453" s="9"/>
       <c r="H453" s="9" t="s">
         <v>50</v>
       </c>
@@ -28058,9 +27839,7 @@
       <c r="F454" s="13" t="s">
         <v>58</v>
       </c>
-      <c r="G454" s="13" t="s">
-        <v>1995</v>
-      </c>
+      <c r="G454" s="13"/>
       <c r="H454" s="13" t="s">
         <v>50</v>
       </c>
@@ -28091,18 +27870,14 @@
       <c r="C455" s="9">
         <v>6413</v>
       </c>
-      <c r="D455" s="10" t="s">
-        <v>1995</v>
-      </c>
+      <c r="D455" s="10"/>
       <c r="E455" s="9" t="s">
         <v>47</v>
       </c>
       <c r="F455" s="9" t="s">
         <v>58</v>
       </c>
-      <c r="G455" s="9" t="s">
-        <v>1995</v>
-      </c>
+      <c r="G455" s="9"/>
       <c r="H455" s="9" t="s">
         <v>50</v>
       </c>
@@ -28133,18 +27908,14 @@
       <c r="C456" s="13">
         <v>120</v>
       </c>
-      <c r="D456" s="14" t="s">
-        <v>1995</v>
-      </c>
+      <c r="D456" s="14"/>
       <c r="E456" s="13" t="s">
         <v>47</v>
       </c>
       <c r="F456" s="13" t="s">
         <v>58</v>
       </c>
-      <c r="G456" s="13" t="s">
-        <v>1995</v>
-      </c>
+      <c r="G456" s="13"/>
       <c r="H456" s="13" t="s">
         <v>50</v>
       </c>
@@ -28175,18 +27946,14 @@
       <c r="C457" s="9">
         <v>6431</v>
       </c>
-      <c r="D457" s="10" t="s">
-        <v>1995</v>
-      </c>
+      <c r="D457" s="10"/>
       <c r="E457" s="9" t="s">
         <v>47</v>
       </c>
       <c r="F457" s="9" t="s">
         <v>58</v>
       </c>
-      <c r="G457" s="9" t="s">
-        <v>1995</v>
-      </c>
+      <c r="G457" s="9"/>
       <c r="H457" s="9" t="s">
         <v>50</v>
       </c>
@@ -28217,18 +27984,14 @@
       <c r="C458" s="13">
         <v>126</v>
       </c>
-      <c r="D458" s="14" t="s">
-        <v>1995</v>
-      </c>
+      <c r="D458" s="14"/>
       <c r="E458" s="13" t="s">
         <v>47</v>
       </c>
       <c r="F458" s="13" t="s">
         <v>58</v>
       </c>
-      <c r="G458" s="13" t="s">
-        <v>1995</v>
-      </c>
+      <c r="G458" s="13"/>
       <c r="H458" s="13" t="s">
         <v>50</v>
       </c>
@@ -28259,18 +28022,14 @@
       <c r="C459" s="9">
         <v>97</v>
       </c>
-      <c r="D459" s="10" t="s">
-        <v>1995</v>
-      </c>
+      <c r="D459" s="10"/>
       <c r="E459" s="9" t="s">
         <v>47</v>
       </c>
       <c r="F459" s="9" t="s">
         <v>58</v>
       </c>
-      <c r="G459" s="9" t="s">
-        <v>1995</v>
-      </c>
+      <c r="G459" s="9"/>
       <c r="H459" s="9" t="s">
         <v>50</v>
       </c>
@@ -28301,18 +28060,14 @@
       <c r="C460" s="13">
         <v>6463</v>
       </c>
-      <c r="D460" s="14" t="s">
-        <v>1995</v>
-      </c>
+      <c r="D460" s="14"/>
       <c r="E460" s="13" t="s">
         <v>47</v>
       </c>
       <c r="F460" s="13" t="s">
         <v>58</v>
       </c>
-      <c r="G460" s="13" t="s">
-        <v>1995</v>
-      </c>
+      <c r="G460" s="13"/>
       <c r="H460" s="13" t="s">
         <v>50</v>
       </c>
@@ -28343,18 +28098,14 @@
       <c r="C461" s="9">
         <v>6308</v>
       </c>
-      <c r="D461" s="10" t="s">
-        <v>1995</v>
-      </c>
+      <c r="D461" s="10"/>
       <c r="E461" s="9" t="s">
         <v>47</v>
       </c>
       <c r="F461" s="9" t="s">
         <v>58</v>
       </c>
-      <c r="G461" s="9" t="s">
-        <v>1995</v>
-      </c>
+      <c r="G461" s="9"/>
       <c r="H461" s="9" t="s">
         <v>50</v>
       </c>
@@ -28385,18 +28136,14 @@
       <c r="C462" s="13">
         <v>6212</v>
       </c>
-      <c r="D462" s="14" t="s">
-        <v>1995</v>
-      </c>
+      <c r="D462" s="14"/>
       <c r="E462" s="13" t="s">
         <v>47</v>
       </c>
       <c r="F462" s="13" t="s">
         <v>58</v>
       </c>
-      <c r="G462" s="13" t="s">
-        <v>1995</v>
-      </c>
+      <c r="G462" s="13"/>
       <c r="H462" s="13" t="s">
         <v>50</v>
       </c>
@@ -28427,18 +28174,14 @@
       <c r="C463" s="9">
         <v>6235</v>
       </c>
-      <c r="D463" s="10" t="s">
-        <v>1995</v>
-      </c>
+      <c r="D463" s="10"/>
       <c r="E463" s="9" t="s">
         <v>47</v>
       </c>
       <c r="F463" s="9" t="s">
         <v>58</v>
       </c>
-      <c r="G463" s="9" t="s">
-        <v>1995</v>
-      </c>
+      <c r="G463" s="9"/>
       <c r="H463" s="9" t="s">
         <v>50</v>
       </c>
@@ -28469,18 +28212,14 @@
       <c r="C464" s="13">
         <v>6287</v>
       </c>
-      <c r="D464" s="14" t="s">
-        <v>1995</v>
-      </c>
+      <c r="D464" s="14"/>
       <c r="E464" s="13" t="s">
         <v>47</v>
       </c>
       <c r="F464" s="13" t="s">
         <v>58</v>
       </c>
-      <c r="G464" s="13" t="s">
-        <v>1995</v>
-      </c>
+      <c r="G464" s="13"/>
       <c r="H464" s="13" t="s">
         <v>50</v>
       </c>
@@ -28511,18 +28250,14 @@
       <c r="C465" s="9">
         <v>6142</v>
       </c>
-      <c r="D465" s="10" t="s">
-        <v>1995</v>
-      </c>
+      <c r="D465" s="10"/>
       <c r="E465" s="9" t="s">
         <v>47</v>
       </c>
       <c r="F465" s="9" t="s">
         <v>58</v>
       </c>
-      <c r="G465" s="9" t="s">
-        <v>1995</v>
-      </c>
+      <c r="G465" s="9"/>
       <c r="H465" s="9" t="s">
         <v>50</v>
       </c>
@@ -28553,18 +28288,14 @@
       <c r="C466" s="13">
         <v>6293</v>
       </c>
-      <c r="D466" s="14" t="s">
-        <v>1995</v>
-      </c>
+      <c r="D466" s="14"/>
       <c r="E466" s="13" t="s">
         <v>47</v>
       </c>
       <c r="F466" s="13" t="s">
         <v>58</v>
       </c>
-      <c r="G466" s="13" t="s">
-        <v>1995</v>
-      </c>
+      <c r="G466" s="13"/>
       <c r="H466" s="13" t="s">
         <v>50</v>
       </c>
@@ -28595,18 +28326,14 @@
       <c r="C467" s="9">
         <v>6383</v>
       </c>
-      <c r="D467" s="10" t="s">
-        <v>1995</v>
-      </c>
+      <c r="D467" s="10"/>
       <c r="E467" s="9" t="s">
         <v>47</v>
       </c>
       <c r="F467" s="9" t="s">
         <v>58</v>
       </c>
-      <c r="G467" s="9" t="s">
-        <v>1995</v>
-      </c>
+      <c r="G467" s="9"/>
       <c r="H467" s="9" t="s">
         <v>50</v>
       </c>
@@ -28637,18 +28364,14 @@
       <c r="C468" s="13">
         <v>6322</v>
       </c>
-      <c r="D468" s="14" t="s">
-        <v>1995</v>
-      </c>
+      <c r="D468" s="14"/>
       <c r="E468" s="13" t="s">
         <v>47</v>
       </c>
       <c r="F468" s="13" t="s">
         <v>58</v>
       </c>
-      <c r="G468" s="13" t="s">
-        <v>1995</v>
-      </c>
+      <c r="G468" s="13"/>
       <c r="H468" s="13" t="s">
         <v>50</v>
       </c>
@@ -28679,18 +28402,14 @@
       <c r="C469" s="9">
         <v>6180</v>
       </c>
-      <c r="D469" s="10" t="s">
-        <v>1995</v>
-      </c>
+      <c r="D469" s="10"/>
       <c r="E469" s="9" t="s">
         <v>47</v>
       </c>
       <c r="F469" s="9" t="s">
         <v>58</v>
       </c>
-      <c r="G469" s="9" t="s">
-        <v>1995</v>
-      </c>
+      <c r="G469" s="9"/>
       <c r="H469" s="9" t="s">
         <v>50</v>
       </c>
@@ -28721,18 +28440,14 @@
       <c r="C470" s="13">
         <v>6245</v>
       </c>
-      <c r="D470" s="14" t="s">
-        <v>1995</v>
-      </c>
+      <c r="D470" s="14"/>
       <c r="E470" s="13" t="s">
         <v>47</v>
       </c>
       <c r="F470" s="13" t="s">
         <v>58</v>
       </c>
-      <c r="G470" s="13" t="s">
-        <v>1995</v>
-      </c>
+      <c r="G470" s="13"/>
       <c r="H470" s="13" t="s">
         <v>50</v>
       </c>
@@ -28763,18 +28478,14 @@
       <c r="C471" s="9">
         <v>6240</v>
       </c>
-      <c r="D471" s="10" t="s">
-        <v>1995</v>
-      </c>
+      <c r="D471" s="10"/>
       <c r="E471" s="9" t="s">
         <v>47</v>
       </c>
       <c r="F471" s="9" t="s">
         <v>58</v>
       </c>
-      <c r="G471" s="9" t="s">
-        <v>1995</v>
-      </c>
+      <c r="G471" s="9"/>
       <c r="H471" s="9" t="s">
         <v>50</v>
       </c>
@@ -28805,18 +28516,14 @@
       <c r="C472" s="13">
         <v>6191</v>
       </c>
-      <c r="D472" s="14" t="s">
-        <v>1995</v>
-      </c>
+      <c r="D472" s="14"/>
       <c r="E472" s="13" t="s">
         <v>47</v>
       </c>
       <c r="F472" s="13" t="s">
         <v>58</v>
       </c>
-      <c r="G472" s="13" t="s">
-        <v>1995</v>
-      </c>
+      <c r="G472" s="13"/>
       <c r="H472" s="13" t="s">
         <v>50</v>
       </c>
@@ -28847,18 +28554,14 @@
       <c r="C473" s="9">
         <v>6405</v>
       </c>
-      <c r="D473" s="10" t="s">
-        <v>1995</v>
-      </c>
+      <c r="D473" s="10"/>
       <c r="E473" s="9" t="s">
         <v>47</v>
       </c>
       <c r="F473" s="9" t="s">
         <v>58</v>
       </c>
-      <c r="G473" s="9" t="s">
-        <v>1995</v>
-      </c>
+      <c r="G473" s="9"/>
       <c r="H473" s="9" t="s">
         <v>50</v>
       </c>
@@ -28889,18 +28592,14 @@
       <c r="C474" s="13">
         <v>6214</v>
       </c>
-      <c r="D474" s="14" t="s">
-        <v>1995</v>
-      </c>
+      <c r="D474" s="14"/>
       <c r="E474" s="13" t="s">
         <v>47</v>
       </c>
       <c r="F474" s="13" t="s">
         <v>58</v>
       </c>
-      <c r="G474" s="13" t="s">
-        <v>1995</v>
-      </c>
+      <c r="G474" s="13"/>
       <c r="H474" s="13" t="s">
         <v>50</v>
       </c>
@@ -28931,18 +28630,14 @@
       <c r="C475" s="9">
         <v>6412</v>
       </c>
-      <c r="D475" s="10" t="s">
-        <v>1995</v>
-      </c>
+      <c r="D475" s="10"/>
       <c r="E475" s="9" t="s">
         <v>47</v>
       </c>
       <c r="F475" s="9" t="s">
         <v>58</v>
       </c>
-      <c r="G475" s="9" t="s">
-        <v>1995</v>
-      </c>
+      <c r="G475" s="9"/>
       <c r="H475" s="9" t="s">
         <v>50</v>
       </c>
@@ -28973,18 +28668,14 @@
       <c r="C476" s="13">
         <v>6441</v>
       </c>
-      <c r="D476" s="14" t="s">
-        <v>1995</v>
-      </c>
+      <c r="D476" s="14"/>
       <c r="E476" s="13" t="s">
         <v>47</v>
       </c>
       <c r="F476" s="13" t="s">
         <v>58</v>
       </c>
-      <c r="G476" s="13" t="s">
-        <v>1995</v>
-      </c>
+      <c r="G476" s="13"/>
       <c r="H476" s="13" t="s">
         <v>50</v>
       </c>
@@ -29015,18 +28706,14 @@
       <c r="C477" s="9">
         <v>6349</v>
       </c>
-      <c r="D477" s="10" t="s">
-        <v>1995</v>
-      </c>
+      <c r="D477" s="10"/>
       <c r="E477" s="9" t="s">
         <v>47</v>
       </c>
       <c r="F477" s="9" t="s">
         <v>58</v>
       </c>
-      <c r="G477" s="9" t="s">
-        <v>1995</v>
-      </c>
+      <c r="G477" s="9"/>
       <c r="H477" s="9" t="s">
         <v>50</v>
       </c>
@@ -29057,18 +28744,14 @@
       <c r="C478" s="13">
         <v>6148</v>
       </c>
-      <c r="D478" s="14" t="s">
-        <v>1995</v>
-      </c>
+      <c r="D478" s="14"/>
       <c r="E478" s="13" t="s">
         <v>47</v>
       </c>
       <c r="F478" s="13" t="s">
         <v>58</v>
       </c>
-      <c r="G478" s="13" t="s">
-        <v>1995</v>
-      </c>
+      <c r="G478" s="13"/>
       <c r="H478" s="13" t="s">
         <v>50</v>
       </c>
@@ -29099,18 +28782,14 @@
       <c r="C479" s="9">
         <v>94</v>
       </c>
-      <c r="D479" s="10" t="s">
-        <v>1995</v>
-      </c>
+      <c r="D479" s="10"/>
       <c r="E479" s="9" t="s">
         <v>47</v>
       </c>
       <c r="F479" s="9" t="s">
         <v>58</v>
       </c>
-      <c r="G479" s="9" t="s">
-        <v>1995</v>
-      </c>
+      <c r="G479" s="9"/>
       <c r="H479" s="9" t="s">
         <v>50</v>
       </c>
@@ -29141,18 +28820,14 @@
       <c r="C480" s="13">
         <v>99</v>
       </c>
-      <c r="D480" s="14" t="s">
-        <v>1995</v>
-      </c>
+      <c r="D480" s="14"/>
       <c r="E480" s="13" t="s">
         <v>47</v>
       </c>
       <c r="F480" s="13" t="s">
         <v>58</v>
       </c>
-      <c r="G480" s="13" t="s">
-        <v>1995</v>
-      </c>
+      <c r="G480" s="13"/>
       <c r="H480" s="13" t="s">
         <v>50</v>
       </c>
@@ -29183,18 +28858,14 @@
       <c r="C481" s="9">
         <v>136</v>
       </c>
-      <c r="D481" s="10" t="s">
-        <v>1995</v>
-      </c>
+      <c r="D481" s="10"/>
       <c r="E481" s="9" t="s">
         <v>47</v>
       </c>
       <c r="F481" s="9" t="s">
         <v>58</v>
       </c>
-      <c r="G481" s="9" t="s">
-        <v>1995</v>
-      </c>
+      <c r="G481" s="9"/>
       <c r="H481" s="9" t="s">
         <v>50</v>
       </c>
@@ -29225,18 +28896,14 @@
       <c r="C482" s="13">
         <v>102</v>
       </c>
-      <c r="D482" s="14" t="s">
-        <v>1995</v>
-      </c>
+      <c r="D482" s="14"/>
       <c r="E482" s="13" t="s">
         <v>47</v>
       </c>
       <c r="F482" s="13" t="s">
         <v>58</v>
       </c>
-      <c r="G482" s="13" t="s">
-        <v>1995</v>
-      </c>
+      <c r="G482" s="13"/>
       <c r="H482" s="13" t="s">
         <v>50</v>
       </c>
@@ -29267,18 +28934,14 @@
       <c r="C483" s="9">
         <v>6367</v>
       </c>
-      <c r="D483" s="10" t="s">
-        <v>1995</v>
-      </c>
+      <c r="D483" s="10"/>
       <c r="E483" s="9" t="s">
         <v>47</v>
       </c>
       <c r="F483" s="9" t="s">
         <v>58</v>
       </c>
-      <c r="G483" s="9" t="s">
-        <v>1995</v>
-      </c>
+      <c r="G483" s="9"/>
       <c r="H483" s="9" t="s">
         <v>50</v>
       </c>
@@ -29903,9 +29566,7 @@
       <c r="M495" s="21">
         <v>43567</v>
       </c>
-      <c r="N495" s="21" t="s">
-        <v>1995</v>
-      </c>
+      <c r="N495" s="21"/>
       <c r="O495" s="21"/>
       <c r="P495" s="21"/>
       <c r="Q495" s="21"/>
@@ -30121,9 +29782,7 @@
       <c r="C500" s="23">
         <v>271</v>
       </c>
-      <c r="D500" s="24" t="s">
-        <v>1995</v>
-      </c>
+      <c r="D500" s="24"/>
       <c r="E500" s="23" t="s">
         <v>175</v>
       </c>
@@ -30167,9 +29826,7 @@
       <c r="C501" s="16">
         <v>282</v>
       </c>
-      <c r="D501" s="21" t="s">
-        <v>1995</v>
-      </c>
+      <c r="D501" s="21"/>
       <c r="E501" s="16" t="s">
         <v>175</v>
       </c>
@@ -30239,9 +29896,7 @@
       <c r="M502" s="24">
         <v>43691</v>
       </c>
-      <c r="N502" s="24" t="s">
-        <v>1995</v>
-      </c>
+      <c r="N502" s="24"/>
       <c r="O502" s="24"/>
       <c r="P502" s="24"/>
       <c r="Q502" s="24"/>
@@ -30493,9 +30148,7 @@
       <c r="C507" s="16">
         <v>250</v>
       </c>
-      <c r="D507" s="21" t="s">
-        <v>1995</v>
-      </c>
+      <c r="D507" s="21"/>
       <c r="E507" s="16" t="s">
         <v>175</v>
       </c>
@@ -30541,9 +30194,7 @@
       <c r="C508" s="23">
         <v>241</v>
       </c>
-      <c r="D508" s="24" t="s">
-        <v>1995</v>
-      </c>
+      <c r="D508" s="24"/>
       <c r="E508" s="23" t="s">
         <v>175</v>
       </c>
@@ -30731,9 +30382,7 @@
       <c r="C512" s="23">
         <v>290</v>
       </c>
-      <c r="D512" s="24" t="s">
-        <v>1995</v>
-      </c>
+      <c r="D512" s="24"/>
       <c r="E512" s="23" t="s">
         <v>175</v>
       </c>
@@ -30951,9 +30600,7 @@
       <c r="C516" s="13">
         <v>263</v>
       </c>
-      <c r="D516" s="14" t="s">
-        <v>1995</v>
-      </c>
+      <c r="D516" s="14"/>
       <c r="E516" s="13" t="s">
         <v>175</v>
       </c>
@@ -30995,9 +30642,7 @@
       <c r="C517" s="9">
         <v>328</v>
       </c>
-      <c r="D517" s="10" t="s">
-        <v>1995</v>
-      </c>
+      <c r="D517" s="10"/>
       <c r="E517" s="9" t="s">
         <v>175</v>
       </c>
@@ -31209,9 +30854,7 @@
       <c r="C521" s="9">
         <v>224</v>
       </c>
-      <c r="D521" s="10" t="s">
-        <v>1995</v>
-      </c>
+      <c r="D521" s="10"/>
       <c r="E521" s="9" t="s">
         <v>175</v>
       </c>
@@ -31255,9 +30898,7 @@
       <c r="C522" s="13">
         <v>299</v>
       </c>
-      <c r="D522" s="14" t="s">
-        <v>1995</v>
-      </c>
+      <c r="D522" s="14"/>
       <c r="E522" s="13" t="s">
         <v>175</v>
       </c>
@@ -31301,9 +30942,7 @@
       <c r="C523" s="9">
         <v>549</v>
       </c>
-      <c r="D523" s="10" t="s">
-        <v>1995</v>
-      </c>
+      <c r="D523" s="10"/>
       <c r="E523" s="9" t="s">
         <v>175</v>
       </c>
@@ -31351,9 +30990,7 @@
       <c r="C524" s="13">
         <v>276</v>
       </c>
-      <c r="D524" s="14" t="s">
-        <v>1995</v>
-      </c>
+      <c r="D524" s="14"/>
       <c r="E524" s="13" t="s">
         <v>175</v>
       </c>
@@ -31665,9 +31302,7 @@
       <c r="C530" s="13">
         <v>232</v>
       </c>
-      <c r="D530" s="14" t="s">
-        <v>1995</v>
-      </c>
+      <c r="D530" s="14"/>
       <c r="E530" s="13" t="s">
         <v>175</v>
       </c>
@@ -31807,9 +31442,7 @@
       <c r="C533" s="9">
         <v>324</v>
       </c>
-      <c r="D533" s="10" t="s">
-        <v>1995</v>
-      </c>
+      <c r="D533" s="10"/>
       <c r="E533" s="9" t="s">
         <v>175</v>
       </c>
@@ -31853,9 +31486,7 @@
       <c r="C534" s="13">
         <v>267</v>
       </c>
-      <c r="D534" s="14" t="s">
-        <v>1995</v>
-      </c>
+      <c r="D534" s="14"/>
       <c r="E534" s="13" t="s">
         <v>175</v>
       </c>
@@ -31903,9 +31534,7 @@
       <c r="C535" s="9">
         <v>197</v>
       </c>
-      <c r="D535" s="10" t="s">
-        <v>1995</v>
-      </c>
+      <c r="D535" s="10"/>
       <c r="E535" s="9" t="s">
         <v>175</v>
       </c>
@@ -32215,9 +31844,7 @@
       <c r="C541" s="9">
         <v>243</v>
       </c>
-      <c r="D541" s="10" t="s">
-        <v>1995</v>
-      </c>
+      <c r="D541" s="10"/>
       <c r="E541" s="9" t="s">
         <v>175</v>
       </c>
@@ -32311,9 +31938,7 @@
       <c r="C543" s="9">
         <v>316</v>
       </c>
-      <c r="D543" s="10" t="s">
-        <v>1995</v>
-      </c>
+      <c r="D543" s="10"/>
       <c r="E543" s="9" t="s">
         <v>175</v>
       </c>
@@ -32355,9 +31980,7 @@
       <c r="C544" s="13">
         <v>254</v>
       </c>
-      <c r="D544" s="14" t="s">
-        <v>1995</v>
-      </c>
+      <c r="D544" s="14"/>
       <c r="E544" s="13" t="s">
         <v>175</v>
       </c>
@@ -32605,9 +32228,7 @@
       <c r="C549" s="9">
         <v>347</v>
       </c>
-      <c r="D549" s="10" t="s">
-        <v>1995</v>
-      </c>
+      <c r="D549" s="10"/>
       <c r="E549" s="9" t="s">
         <v>175</v>
       </c>
@@ -32809,9 +32430,7 @@
       <c r="C553" s="9">
         <v>298</v>
       </c>
-      <c r="D553" s="10" t="s">
-        <v>1995</v>
-      </c>
+      <c r="D553" s="10"/>
       <c r="E553" s="9" t="s">
         <v>175</v>
       </c>
@@ -33139,9 +32758,7 @@
       <c r="C560" s="13">
         <v>388</v>
       </c>
-      <c r="D560" s="14" t="s">
-        <v>1995</v>
-      </c>
+      <c r="D560" s="14"/>
       <c r="E560" s="13" t="s">
         <v>175</v>
       </c>
@@ -33231,9 +32848,7 @@
       <c r="C562" s="13">
         <v>377</v>
       </c>
-      <c r="D562" s="14" t="s">
-        <v>1995</v>
-      </c>
+      <c r="D562" s="14"/>
       <c r="E562" s="13" t="s">
         <v>175</v>
       </c>
@@ -33413,9 +33028,7 @@
       <c r="C566" s="13">
         <v>287</v>
       </c>
-      <c r="D566" s="14" t="s">
-        <v>1995</v>
-      </c>
+      <c r="D566" s="14"/>
       <c r="E566" s="13" t="s">
         <v>175</v>
       </c>
@@ -33537,9 +33150,7 @@
       <c r="M568" s="14">
         <v>43996</v>
       </c>
-      <c r="N568" s="14" t="s">
-        <v>1995</v>
-      </c>
+      <c r="N568" s="14"/>
       <c r="O568" s="14"/>
       <c r="P568" s="14"/>
       <c r="Q568" s="14">
@@ -33713,9 +33324,7 @@
       <c r="C572" s="13">
         <v>358</v>
       </c>
-      <c r="D572" s="14" t="s">
-        <v>1995</v>
-      </c>
+      <c r="D572" s="14"/>
       <c r="E572" s="13" t="s">
         <v>175</v>
       </c>
@@ -33807,9 +33416,7 @@
       <c r="C574" s="13">
         <v>333</v>
       </c>
-      <c r="D574" s="14" t="s">
-        <v>1995</v>
-      </c>
+      <c r="D574" s="14"/>
       <c r="E574" s="13" t="s">
         <v>175</v>
       </c>
@@ -34381,9 +33988,7 @@
       <c r="C585" s="9">
         <v>446</v>
       </c>
-      <c r="D585" s="10" t="s">
-        <v>1995</v>
-      </c>
+      <c r="D585" s="10"/>
       <c r="E585" s="9" t="s">
         <v>175</v>
       </c>
@@ -34521,9 +34126,7 @@
       <c r="C588" s="13">
         <v>415</v>
       </c>
-      <c r="D588" s="14" t="s">
-        <v>1995</v>
-      </c>
+      <c r="D588" s="14"/>
       <c r="E588" s="13" t="s">
         <v>175</v>
       </c>
@@ -34571,9 +34174,7 @@
       <c r="C589" s="9">
         <v>425</v>
       </c>
-      <c r="D589" s="10" t="s">
-        <v>1995</v>
-      </c>
+      <c r="D589" s="10"/>
       <c r="E589" s="9" t="s">
         <v>175</v>
       </c>
@@ -35007,9 +34608,7 @@
       <c r="C597" s="9">
         <v>203</v>
       </c>
-      <c r="D597" s="10" t="s">
-        <v>1995</v>
-      </c>
+      <c r="D597" s="10"/>
       <c r="E597" s="9" t="s">
         <v>175</v>
       </c>
@@ -35301,9 +34900,7 @@
       <c r="C603" s="9">
         <v>382</v>
       </c>
-      <c r="D603" s="10" t="s">
-        <v>1995</v>
-      </c>
+      <c r="D603" s="10"/>
       <c r="E603" s="9" t="s">
         <v>175</v>
       </c>
@@ -35441,9 +35038,7 @@
       <c r="C606" s="13">
         <v>211</v>
       </c>
-      <c r="D606" s="14" t="s">
-        <v>1995</v>
-      </c>
+      <c r="D606" s="14"/>
       <c r="E606" s="13" t="s">
         <v>175</v>
       </c>
@@ -35533,9 +35128,7 @@
       <c r="C608" s="13">
         <v>568</v>
       </c>
-      <c r="D608" s="14" t="s">
-        <v>1995</v>
-      </c>
+      <c r="D608" s="14"/>
       <c r="E608" s="13" t="s">
         <v>175</v>
       </c>
@@ -35633,9 +35226,7 @@
       <c r="C610" s="13">
         <v>329</v>
       </c>
-      <c r="D610" s="14" t="s">
-        <v>1995</v>
-      </c>
+      <c r="D610" s="14"/>
       <c r="E610" s="13" t="s">
         <v>175</v>
       </c>
@@ -35723,9 +35314,7 @@
       <c r="C612" s="13">
         <v>354</v>
       </c>
-      <c r="D612" s="14" t="s">
-        <v>1995</v>
-      </c>
+      <c r="D612" s="14"/>
       <c r="E612" s="13" t="s">
         <v>175</v>
       </c>
@@ -35767,9 +35356,7 @@
       <c r="C613" s="9">
         <v>352</v>
       </c>
-      <c r="D613" s="10" t="s">
-        <v>1995</v>
-      </c>
+      <c r="D613" s="10"/>
       <c r="E613" s="9" t="s">
         <v>175</v>
       </c>
@@ -35813,9 +35400,7 @@
       <c r="C614" s="13">
         <v>340</v>
       </c>
-      <c r="D614" s="14" t="s">
-        <v>1995</v>
-      </c>
+      <c r="D614" s="14"/>
       <c r="E614" s="13" t="s">
         <v>175</v>
       </c>
@@ -35967,9 +35552,7 @@
       <c r="C617" s="9">
         <v>289</v>
       </c>
-      <c r="D617" s="10" t="s">
-        <v>1995</v>
-      </c>
+      <c r="D617" s="10"/>
       <c r="E617" s="9" t="s">
         <v>175</v>
       </c>
@@ -36067,9 +35650,7 @@
       <c r="C619" s="9">
         <v>570</v>
       </c>
-      <c r="D619" s="10" t="s">
-        <v>1995</v>
-      </c>
+      <c r="D619" s="10"/>
       <c r="E619" s="9" t="s">
         <v>175</v>
       </c>
@@ -36215,9 +35796,7 @@
       <c r="C622" s="13">
         <v>559</v>
       </c>
-      <c r="D622" s="14" t="s">
-        <v>1995</v>
-      </c>
+      <c r="D622" s="14"/>
       <c r="E622" s="13" t="s">
         <v>175</v>
       </c>
@@ -36263,9 +35842,7 @@
       <c r="C623" s="9">
         <v>531</v>
       </c>
-      <c r="D623" s="10" t="s">
-        <v>1995</v>
-      </c>
+      <c r="D623" s="10"/>
       <c r="E623" s="9" t="s">
         <v>175</v>
       </c>
@@ -36307,9 +35884,7 @@
       <c r="C624" s="13">
         <v>375</v>
       </c>
-      <c r="D624" s="14" t="s">
-        <v>1995</v>
-      </c>
+      <c r="D624" s="14"/>
       <c r="E624" s="13" t="s">
         <v>175</v>
       </c>
@@ -36353,9 +35928,7 @@
       <c r="C625" s="9">
         <v>323</v>
       </c>
-      <c r="D625" s="10" t="s">
-        <v>1995</v>
-      </c>
+      <c r="D625" s="10"/>
       <c r="E625" s="9" t="s">
         <v>175</v>
       </c>
@@ -36449,9 +36022,7 @@
       <c r="C627" s="9">
         <v>454</v>
       </c>
-      <c r="D627" s="10" t="s">
-        <v>1995</v>
-      </c>
+      <c r="D627" s="10"/>
       <c r="E627" s="9" t="s">
         <v>175</v>
       </c>
@@ -36497,9 +36068,7 @@
       <c r="C628" s="13">
         <v>579</v>
       </c>
-      <c r="D628" s="14" t="s">
-        <v>1995</v>
-      </c>
+      <c r="D628" s="14"/>
       <c r="E628" s="13" t="s">
         <v>175</v>
       </c>
@@ -36811,9 +36380,7 @@
       <c r="C634" s="13">
         <v>598</v>
       </c>
-      <c r="D634" s="14" t="s">
-        <v>1995</v>
-      </c>
+      <c r="D634" s="14"/>
       <c r="E634" s="13" t="s">
         <v>175</v>
       </c>
@@ -36961,9 +36528,7 @@
       <c r="C637" s="9">
         <v>420</v>
       </c>
-      <c r="D637" s="10" t="s">
-        <v>1995</v>
-      </c>
+      <c r="D637" s="10"/>
       <c r="E637" s="9" t="s">
         <v>175</v>
       </c>
@@ -37005,9 +36570,7 @@
       <c r="C638" s="13">
         <v>563</v>
       </c>
-      <c r="D638" s="14" t="s">
-        <v>1995</v>
-      </c>
+      <c r="D638" s="14"/>
       <c r="E638" s="13" t="s">
         <v>175</v>
       </c>
@@ -37101,9 +36664,7 @@
       <c r="C640" s="13">
         <v>313</v>
       </c>
-      <c r="D640" s="14" t="s">
-        <v>1995</v>
-      </c>
+      <c r="D640" s="14"/>
       <c r="E640" s="13" t="s">
         <v>175</v>
       </c>
@@ -37149,9 +36710,7 @@
       <c r="C641" s="9">
         <v>462</v>
       </c>
-      <c r="D641" s="10" t="s">
-        <v>1995</v>
-      </c>
+      <c r="D641" s="10"/>
       <c r="E641" s="9" t="s">
         <v>175</v>
       </c>
@@ -37195,9 +36754,7 @@
       <c r="C642" s="13">
         <v>603</v>
       </c>
-      <c r="D642" s="14" t="s">
-        <v>1995</v>
-      </c>
+      <c r="D642" s="14"/>
       <c r="E642" s="13" t="s">
         <v>175</v>
       </c>
@@ -37245,9 +36802,7 @@
       <c r="C643" s="9">
         <v>6022</v>
       </c>
-      <c r="D643" s="10" t="s">
-        <v>1995</v>
-      </c>
+      <c r="D643" s="10"/>
       <c r="E643" s="9" t="s">
         <v>175</v>
       </c>
@@ -37295,9 +36850,7 @@
       <c r="C644" s="13">
         <v>508</v>
       </c>
-      <c r="D644" s="14" t="s">
-        <v>1995</v>
-      </c>
+      <c r="D644" s="14"/>
       <c r="E644" s="13" t="s">
         <v>175</v>
       </c>
@@ -37389,9 +36942,7 @@
       <c r="C646" s="23">
         <v>397</v>
       </c>
-      <c r="D646" s="24" t="s">
-        <v>1995</v>
-      </c>
+      <c r="D646" s="24"/>
       <c r="E646" s="23" t="s">
         <v>175</v>
       </c>
@@ -37483,9 +37034,7 @@
       <c r="C648" s="13">
         <v>356</v>
       </c>
-      <c r="D648" s="14" t="s">
-        <v>1995</v>
-      </c>
+      <c r="D648" s="14"/>
       <c r="E648" s="13" t="s">
         <v>175</v>
       </c>
@@ -37527,9 +37076,7 @@
       <c r="C649" s="9">
         <v>320</v>
       </c>
-      <c r="D649" s="10" t="s">
-        <v>1995</v>
-      </c>
+      <c r="D649" s="10"/>
       <c r="E649" s="9" t="s">
         <v>175</v>
       </c>
@@ -37573,9 +37120,7 @@
       <c r="C650" s="13">
         <v>310</v>
       </c>
-      <c r="D650" s="14" t="s">
-        <v>1995</v>
-      </c>
+      <c r="D650" s="14"/>
       <c r="E650" s="13" t="s">
         <v>175</v>
       </c>
@@ -37905,9 +37450,7 @@
       <c r="M656" s="14">
         <v>43339</v>
       </c>
-      <c r="N656" s="14" t="s">
-        <v>1995</v>
-      </c>
+      <c r="N656" s="14"/>
       <c r="O656" s="14"/>
       <c r="P656" s="14">
         <v>44464</v>
@@ -38337,9 +37880,7 @@
       <c r="C665" s="9">
         <v>490</v>
       </c>
-      <c r="D665" s="10" t="s">
-        <v>1995</v>
-      </c>
+      <c r="D665" s="10"/>
       <c r="E665" s="9" t="s">
         <v>175</v>
       </c>
@@ -38387,9 +37928,7 @@
       <c r="C666" s="13">
         <v>381</v>
       </c>
-      <c r="D666" s="14" t="s">
-        <v>1995</v>
-      </c>
+      <c r="D666" s="14"/>
       <c r="E666" s="13" t="s">
         <v>175</v>
       </c>
@@ -38431,9 +37970,7 @@
       <c r="C667" s="9">
         <v>408</v>
       </c>
-      <c r="D667" s="10" t="s">
-        <v>1995</v>
-      </c>
+      <c r="D667" s="10"/>
       <c r="E667" s="9" t="s">
         <v>175</v>
       </c>
@@ -38477,9 +38014,7 @@
       <c r="C668" s="13">
         <v>204</v>
       </c>
-      <c r="D668" s="14" t="s">
-        <v>1995</v>
-      </c>
+      <c r="D668" s="14"/>
       <c r="E668" s="13" t="s">
         <v>175</v>
       </c>
@@ -38521,9 +38056,7 @@
       <c r="C669" s="9">
         <v>468</v>
       </c>
-      <c r="D669" s="10" t="s">
-        <v>1995</v>
-      </c>
+      <c r="D669" s="10"/>
       <c r="E669" s="9" t="s">
         <v>175</v>
       </c>
@@ -38569,9 +38102,7 @@
       <c r="C670" s="13">
         <v>506</v>
       </c>
-      <c r="D670" s="14" t="s">
-        <v>1995</v>
-      </c>
+      <c r="D670" s="14"/>
       <c r="E670" s="13" t="s">
         <v>175</v>
       </c>
@@ -38615,9 +38146,7 @@
       <c r="C671" s="9">
         <v>435</v>
       </c>
-      <c r="D671" s="10" t="s">
-        <v>1995</v>
-      </c>
+      <c r="D671" s="10"/>
       <c r="E671" s="9" t="s">
         <v>175</v>
       </c>
@@ -38661,9 +38190,7 @@
       <c r="C672" s="13">
         <v>509</v>
       </c>
-      <c r="D672" s="14" t="s">
-        <v>1995</v>
-      </c>
+      <c r="D672" s="14"/>
       <c r="E672" s="13" t="s">
         <v>175</v>
       </c>
@@ -38709,9 +38236,7 @@
       <c r="C673" s="9">
         <v>620</v>
       </c>
-      <c r="D673" s="10" t="s">
-        <v>1995</v>
-      </c>
+      <c r="D673" s="10"/>
       <c r="E673" s="9" t="s">
         <v>175</v>
       </c>
@@ -38755,9 +38280,7 @@
       <c r="C674" s="13">
         <v>567</v>
       </c>
-      <c r="D674" s="14" t="s">
-        <v>1995</v>
-      </c>
+      <c r="D674" s="14"/>
       <c r="E674" s="13" t="s">
         <v>175</v>
       </c>
@@ -38803,9 +38326,7 @@
       <c r="C675" s="9">
         <v>585</v>
       </c>
-      <c r="D675" s="10" t="s">
-        <v>1995</v>
-      </c>
+      <c r="D675" s="10"/>
       <c r="E675" s="9" t="s">
         <v>175</v>
       </c>
@@ -38851,9 +38372,7 @@
       <c r="C676" s="13">
         <v>413</v>
       </c>
-      <c r="D676" s="14" t="s">
-        <v>1995</v>
-      </c>
+      <c r="D676" s="14"/>
       <c r="E676" s="13" t="s">
         <v>175</v>
       </c>
@@ -38901,9 +38420,7 @@
       <c r="C677" s="9">
         <v>497</v>
       </c>
-      <c r="D677" s="10" t="s">
-        <v>1995</v>
-      </c>
+      <c r="D677" s="10"/>
       <c r="E677" s="9" t="s">
         <v>175</v>
       </c>
@@ -38949,9 +38466,7 @@
       <c r="C678" s="13">
         <v>488</v>
       </c>
-      <c r="D678" s="14" t="s">
-        <v>1995</v>
-      </c>
+      <c r="D678" s="14"/>
       <c r="E678" s="13" t="s">
         <v>175</v>
       </c>
@@ -39149,9 +38664,7 @@
       <c r="C682" s="13">
         <v>685</v>
       </c>
-      <c r="D682" s="14" t="s">
-        <v>1995</v>
-      </c>
+      <c r="D682" s="14"/>
       <c r="E682" s="13" t="s">
         <v>175</v>
       </c>
@@ -39495,9 +39008,7 @@
       <c r="C689" s="9">
         <v>538</v>
       </c>
-      <c r="D689" s="10" t="s">
-        <v>1995</v>
-      </c>
+      <c r="D689" s="10"/>
       <c r="E689" s="9" t="s">
         <v>175</v>
       </c>
@@ -39543,9 +39054,7 @@
       <c r="C690" s="13">
         <v>533</v>
       </c>
-      <c r="D690" s="14" t="s">
-        <v>1995</v>
-      </c>
+      <c r="D690" s="14"/>
       <c r="E690" s="13" t="s">
         <v>175</v>
       </c>
@@ -39639,9 +39148,7 @@
       <c r="C692" s="13">
         <v>558</v>
       </c>
-      <c r="D692" s="14" t="s">
-        <v>1995</v>
-      </c>
+      <c r="D692" s="14"/>
       <c r="E692" s="13" t="s">
         <v>175</v>
       </c>
@@ -39687,9 +39194,7 @@
       <c r="C693" s="9">
         <v>646</v>
       </c>
-      <c r="D693" s="10" t="s">
-        <v>1995</v>
-      </c>
+      <c r="D693" s="10"/>
       <c r="E693" s="9" t="s">
         <v>175</v>
       </c>
@@ -39735,9 +39240,7 @@
       <c r="C694" s="13">
         <v>355</v>
       </c>
-      <c r="D694" s="14" t="s">
-        <v>1995</v>
-      </c>
+      <c r="D694" s="14"/>
       <c r="E694" s="13" t="s">
         <v>175</v>
       </c>
@@ -39779,9 +39282,7 @@
       <c r="C695" s="9">
         <v>652</v>
       </c>
-      <c r="D695" s="10" t="s">
-        <v>1995</v>
-      </c>
+      <c r="D695" s="10"/>
       <c r="E695" s="9" t="s">
         <v>175</v>
       </c>
@@ -39827,9 +39328,7 @@
       <c r="C696" s="13">
         <v>569</v>
       </c>
-      <c r="D696" s="14" t="s">
-        <v>1995</v>
-      </c>
+      <c r="D696" s="14"/>
       <c r="E696" s="13" t="s">
         <v>175</v>
       </c>
@@ -40393,9 +39892,7 @@
       <c r="C707" s="9">
         <v>679</v>
       </c>
-      <c r="D707" s="10" t="s">
-        <v>1995</v>
-      </c>
+      <c r="D707" s="10"/>
       <c r="E707" s="9" t="s">
         <v>175</v>
       </c>
@@ -40439,9 +39936,7 @@
       <c r="C708" s="13">
         <v>662</v>
       </c>
-      <c r="D708" s="14" t="s">
-        <v>1995</v>
-      </c>
+      <c r="D708" s="14"/>
       <c r="E708" s="13" t="s">
         <v>175</v>
       </c>
@@ -40489,9 +39984,7 @@
       <c r="C709" s="9">
         <v>684</v>
       </c>
-      <c r="D709" s="10" t="s">
-        <v>1995</v>
-      </c>
+      <c r="D709" s="10"/>
       <c r="E709" s="9" t="s">
         <v>175</v>
       </c>
@@ -40539,9 +40032,7 @@
       <c r="C710" s="13">
         <v>678</v>
       </c>
-      <c r="D710" s="14" t="s">
-        <v>1995</v>
-      </c>
+      <c r="D710" s="14"/>
       <c r="E710" s="13" t="s">
         <v>175</v>
       </c>
@@ -41091,9 +40582,7 @@
       <c r="C721" s="9">
         <v>676</v>
       </c>
-      <c r="D721" s="10" t="s">
-        <v>1995</v>
-      </c>
+      <c r="D721" s="10"/>
       <c r="E721" s="9" t="s">
         <v>175</v>
       </c>
@@ -41139,9 +40628,7 @@
       <c r="C722" s="13">
         <v>575</v>
       </c>
-      <c r="D722" s="14" t="s">
-        <v>1995</v>
-      </c>
+      <c r="D722" s="14"/>
       <c r="E722" s="13" t="s">
         <v>175</v>
       </c>
@@ -41187,9 +40674,7 @@
       <c r="C723" s="9">
         <v>351</v>
       </c>
-      <c r="D723" s="10" t="s">
-        <v>1995</v>
-      </c>
+      <c r="D723" s="10"/>
       <c r="E723" s="9" t="s">
         <v>175</v>
       </c>
@@ -41231,9 +40716,7 @@
       <c r="C724" s="13">
         <v>586</v>
       </c>
-      <c r="D724" s="14" t="s">
-        <v>1995</v>
-      </c>
+      <c r="D724" s="14"/>
       <c r="E724" s="13" t="s">
         <v>175</v>
       </c>
@@ -41379,9 +40862,7 @@
       <c r="C727" s="9">
         <v>592</v>
       </c>
-      <c r="D727" s="10" t="s">
-        <v>1995</v>
-      </c>
+      <c r="D727" s="10"/>
       <c r="E727" s="9" t="s">
         <v>175</v>
       </c>
@@ -41427,9 +40908,7 @@
       <c r="C728" s="13">
         <v>593</v>
       </c>
-      <c r="D728" s="14" t="s">
-        <v>1995</v>
-      </c>
+      <c r="D728" s="14"/>
       <c r="E728" s="13" t="s">
         <v>175</v>
       </c>
@@ -41569,9 +41048,7 @@
       <c r="C731" s="9">
         <v>596</v>
       </c>
-      <c r="D731" s="10" t="s">
-        <v>1995</v>
-      </c>
+      <c r="D731" s="10"/>
       <c r="E731" s="9" t="s">
         <v>175</v>
       </c>
@@ -41617,9 +41094,7 @@
       <c r="C732" s="13">
         <v>511</v>
       </c>
-      <c r="D732" s="14" t="s">
-        <v>1995</v>
-      </c>
+      <c r="D732" s="14"/>
       <c r="E732" s="13" t="s">
         <v>175</v>
       </c>
@@ -41665,9 +41140,7 @@
       <c r="C733" s="9">
         <v>626</v>
       </c>
-      <c r="D733" s="10" t="s">
-        <v>1995</v>
-      </c>
+      <c r="D733" s="10"/>
       <c r="E733" s="9" t="s">
         <v>175</v>
       </c>
@@ -42181,9 +41654,7 @@
       <c r="C743" s="9">
         <v>600</v>
       </c>
-      <c r="D743" s="10" t="s">
-        <v>1995</v>
-      </c>
+      <c r="D743" s="10"/>
       <c r="E743" s="9" t="s">
         <v>175</v>
       </c>
@@ -42229,9 +41700,7 @@
       <c r="C744" s="13">
         <v>702</v>
       </c>
-      <c r="D744" s="14" t="s">
-        <v>1995</v>
-      </c>
+      <c r="D744" s="14"/>
       <c r="E744" s="13" t="s">
         <v>175</v>
       </c>
@@ -42277,9 +41746,7 @@
       <c r="C745" s="9">
         <v>701</v>
       </c>
-      <c r="D745" s="10" t="s">
-        <v>1995</v>
-      </c>
+      <c r="D745" s="10"/>
       <c r="E745" s="9" t="s">
         <v>175</v>
       </c>
@@ -42931,9 +42398,7 @@
       <c r="C758" s="13">
         <v>466</v>
       </c>
-      <c r="D758" s="14" t="s">
-        <v>1995</v>
-      </c>
+      <c r="D758" s="14"/>
       <c r="E758" s="13" t="s">
         <v>175</v>
       </c>
@@ -42977,9 +42442,7 @@
       <c r="C759" s="9">
         <v>612</v>
       </c>
-      <c r="D759" s="10" t="s">
-        <v>1995</v>
-      </c>
+      <c r="D759" s="10"/>
       <c r="E759" s="9" t="s">
         <v>175</v>
       </c>
@@ -43025,9 +42488,7 @@
       <c r="C760" s="13">
         <v>539</v>
       </c>
-      <c r="D760" s="14" t="s">
-        <v>1995</v>
-      </c>
+      <c r="D760" s="14"/>
       <c r="E760" s="13" t="s">
         <v>175</v>
       </c>
@@ -43071,9 +42532,7 @@
       <c r="C761" s="9">
         <v>659</v>
       </c>
-      <c r="D761" s="10" t="s">
-        <v>1995</v>
-      </c>
+      <c r="D761" s="10"/>
       <c r="E761" s="9" t="s">
         <v>175</v>
       </c>
@@ -43121,9 +42580,7 @@
       <c r="C762" s="13">
         <v>584</v>
       </c>
-      <c r="D762" s="14" t="s">
-        <v>1995</v>
-      </c>
+      <c r="D762" s="14"/>
       <c r="E762" s="13" t="s">
         <v>175</v>
       </c>
@@ -43169,9 +42626,7 @@
       <c r="C763" s="9">
         <v>614</v>
       </c>
-      <c r="D763" s="10" t="s">
-        <v>1995</v>
-      </c>
+      <c r="D763" s="10"/>
       <c r="E763" s="9" t="s">
         <v>175</v>
       </c>
@@ -43217,9 +42672,7 @@
       <c r="C764" s="13">
         <v>393</v>
       </c>
-      <c r="D764" s="14" t="s">
-        <v>1995</v>
-      </c>
+      <c r="D764" s="14"/>
       <c r="E764" s="13" t="s">
         <v>175</v>
       </c>
@@ -43359,9 +42812,7 @@
       <c r="C767" s="9">
         <v>479</v>
       </c>
-      <c r="D767" s="10" t="s">
-        <v>1995</v>
-      </c>
+      <c r="D767" s="10"/>
       <c r="E767" s="9" t="s">
         <v>175</v>
       </c>
@@ -43405,9 +42856,7 @@
       <c r="C768" s="13">
         <v>405</v>
       </c>
-      <c r="D768" s="14" t="s">
-        <v>1995</v>
-      </c>
+      <c r="D768" s="14"/>
       <c r="E768" s="13" t="s">
         <v>175</v>
       </c>
@@ -43449,9 +42898,7 @@
       <c r="C769" s="9">
         <v>639</v>
       </c>
-      <c r="D769" s="10" t="s">
-        <v>1995</v>
-      </c>
+      <c r="D769" s="10"/>
       <c r="E769" s="9" t="s">
         <v>175</v>
       </c>
@@ -43497,9 +42944,7 @@
       <c r="C770" s="13">
         <v>357</v>
       </c>
-      <c r="D770" s="14" t="s">
-        <v>1995</v>
-      </c>
+      <c r="D770" s="14"/>
       <c r="E770" s="13" t="s">
         <v>175</v>
       </c>
@@ -43587,9 +43032,7 @@
       <c r="C772" s="13">
         <v>644</v>
       </c>
-      <c r="D772" s="14" t="s">
-        <v>1995</v>
-      </c>
+      <c r="D772" s="14"/>
       <c r="E772" s="13" t="s">
         <v>175</v>
       </c>
@@ -43685,9 +43128,7 @@
       <c r="C774" s="13">
         <v>572</v>
       </c>
-      <c r="D774" s="14" t="s">
-        <v>1995</v>
-      </c>
+      <c r="D774" s="14"/>
       <c r="E774" s="13" t="s">
         <v>175</v>
       </c>
@@ -43731,9 +43172,7 @@
       <c r="C775" s="9">
         <v>599</v>
       </c>
-      <c r="D775" s="10" t="s">
-        <v>1995</v>
-      </c>
+      <c r="D775" s="10"/>
       <c r="E775" s="9" t="s">
         <v>175</v>
       </c>
@@ -43779,9 +43218,7 @@
       <c r="C776" s="13">
         <v>615</v>
       </c>
-      <c r="D776" s="14" t="s">
-        <v>1995</v>
-      </c>
+      <c r="D776" s="14"/>
       <c r="E776" s="13" t="s">
         <v>175</v>
       </c>
@@ -43873,9 +43310,7 @@
       <c r="C778" s="13">
         <v>642</v>
       </c>
-      <c r="D778" s="14" t="s">
-        <v>1995</v>
-      </c>
+      <c r="D778" s="14"/>
       <c r="E778" s="13" t="s">
         <v>175</v>
       </c>
@@ -44167,9 +43602,7 @@
       <c r="C784" s="13">
         <v>669</v>
       </c>
-      <c r="D784" s="14" t="s">
-        <v>1995</v>
-      </c>
+      <c r="D784" s="14"/>
       <c r="E784" s="13" t="s">
         <v>175</v>
       </c>
@@ -44215,9 +43648,7 @@
       <c r="C785" s="9">
         <v>647</v>
       </c>
-      <c r="D785" s="10" t="s">
-        <v>1995</v>
-      </c>
+      <c r="D785" s="10"/>
       <c r="E785" s="9" t="s">
         <v>175</v>
       </c>
@@ -44841,9 +44272,7 @@
       <c r="C798" s="13">
         <v>492</v>
       </c>
-      <c r="D798" s="14" t="s">
-        <v>1995</v>
-      </c>
+      <c r="D798" s="14"/>
       <c r="E798" s="13" t="s">
         <v>175</v>
       </c>
@@ -44887,9 +44316,7 @@
       <c r="C799" s="9">
         <v>447</v>
       </c>
-      <c r="D799" s="10" t="s">
-        <v>1995</v>
-      </c>
+      <c r="D799" s="10"/>
       <c r="E799" s="9" t="s">
         <v>175</v>
       </c>
@@ -44937,9 +44364,7 @@
       <c r="C800" s="13">
         <v>682</v>
       </c>
-      <c r="D800" s="14" t="s">
-        <v>1995</v>
-      </c>
+      <c r="D800" s="14"/>
       <c r="E800" s="13" t="s">
         <v>175</v>
       </c>
@@ -44985,18 +44410,14 @@
       <c r="C801" s="9">
         <v>251</v>
       </c>
-      <c r="D801" s="10" t="s">
-        <v>1995</v>
-      </c>
+      <c r="D801" s="10"/>
       <c r="E801" s="9" t="s">
         <v>175</v>
       </c>
       <c r="F801" s="9" t="s">
         <v>48</v>
       </c>
-      <c r="G801" s="9" t="s">
-        <v>1995</v>
-      </c>
+      <c r="G801" s="9"/>
       <c r="H801" s="9" t="s">
         <v>50</v>
       </c>
@@ -45029,18 +44450,14 @@
       <c r="C802" s="13">
         <v>555</v>
       </c>
-      <c r="D802" s="14" t="s">
-        <v>1995</v>
-      </c>
+      <c r="D802" s="14"/>
       <c r="E802" s="13" t="s">
         <v>175</v>
       </c>
       <c r="F802" s="13" t="s">
         <v>48</v>
       </c>
-      <c r="G802" s="13" t="s">
-        <v>1995</v>
-      </c>
+      <c r="G802" s="13"/>
       <c r="H802" s="13" t="s">
         <v>50</v>
       </c>
@@ -45073,18 +44490,14 @@
       <c r="C803" s="9">
         <v>205</v>
       </c>
-      <c r="D803" s="10" t="s">
-        <v>1995</v>
-      </c>
+      <c r="D803" s="10"/>
       <c r="E803" s="9" t="s">
         <v>175</v>
       </c>
       <c r="F803" s="9" t="s">
         <v>53</v>
       </c>
-      <c r="G803" s="9" t="s">
-        <v>1995</v>
-      </c>
+      <c r="G803" s="9"/>
       <c r="H803" s="9" t="s">
         <v>50</v>
       </c>
@@ -45117,18 +44530,14 @@
       <c r="C804" s="13">
         <v>253</v>
       </c>
-      <c r="D804" s="14" t="s">
-        <v>1995</v>
-      </c>
+      <c r="D804" s="14"/>
       <c r="E804" s="13" t="s">
         <v>175</v>
       </c>
       <c r="F804" s="13" t="s">
         <v>53</v>
       </c>
-      <c r="G804" s="13" t="s">
-        <v>1995</v>
-      </c>
+      <c r="G804" s="13"/>
       <c r="H804" s="13" t="s">
         <v>50</v>
       </c>
@@ -45161,18 +44570,14 @@
       <c r="C805" s="9">
         <v>337</v>
       </c>
-      <c r="D805" s="10" t="s">
-        <v>1995</v>
-      </c>
+      <c r="D805" s="10"/>
       <c r="E805" s="9" t="s">
         <v>175</v>
       </c>
       <c r="F805" s="9" t="s">
         <v>53</v>
       </c>
-      <c r="G805" s="9" t="s">
-        <v>1995</v>
-      </c>
+      <c r="G805" s="9"/>
       <c r="H805" s="9" t="s">
         <v>50</v>
       </c>
@@ -45205,18 +44610,14 @@
       <c r="C806" s="13">
         <v>212</v>
       </c>
-      <c r="D806" s="14" t="s">
-        <v>1995</v>
-      </c>
+      <c r="D806" s="14"/>
       <c r="E806" s="13" t="s">
         <v>175</v>
       </c>
       <c r="F806" s="13" t="s">
         <v>58</v>
       </c>
-      <c r="G806" s="13" t="s">
-        <v>1995</v>
-      </c>
+      <c r="G806" s="13"/>
       <c r="H806" s="13" t="s">
         <v>50</v>
       </c>
@@ -45249,18 +44650,14 @@
       <c r="C807" s="9">
         <v>343</v>
       </c>
-      <c r="D807" s="10" t="s">
-        <v>1995</v>
-      </c>
+      <c r="D807" s="10"/>
       <c r="E807" s="9" t="s">
         <v>175</v>
       </c>
       <c r="F807" s="9" t="s">
         <v>58</v>
       </c>
-      <c r="G807" s="9" t="s">
-        <v>1995</v>
-      </c>
+      <c r="G807" s="9"/>
       <c r="H807" s="9" t="s">
         <v>50</v>
       </c>
@@ -45293,18 +44690,14 @@
       <c r="C808" s="23">
         <v>281</v>
       </c>
-      <c r="D808" s="24" t="s">
-        <v>1995</v>
-      </c>
+      <c r="D808" s="24"/>
       <c r="E808" s="23" t="s">
         <v>175</v>
       </c>
       <c r="F808" s="23" t="s">
         <v>58</v>
       </c>
-      <c r="G808" s="23" t="s">
-        <v>1995</v>
-      </c>
+      <c r="G808" s="23"/>
       <c r="H808" s="13" t="s">
         <v>50</v>
       </c>

--- a/data/members.xlsx
+++ b/data/members.xlsx
@@ -454,7 +454,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X810"/>
+  <dimension ref="A1:W811"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -39207,10 +39207,25 @@
       <c r="C810" t="n">
         <v>773</v>
       </c>
-      <c r="E810" t="inlineStr"/>
-      <c r="F810" t="inlineStr"/>
-      <c r="G810" t="inlineStr"/>
-      <c r="H810" t="inlineStr"/>
+    </row>
+    <row r="811">
+      <c r="A811" t="inlineStr">
+        <is>
+          <t>미상(elo_763)</t>
+        </is>
+      </c>
+      <c r="B811" t="inlineStr">
+        <is>
+          <t>elo_763</t>
+        </is>
+      </c>
+      <c r="C811" t="n">
+        <v>763</v>
+      </c>
+      <c r="E811" t="inlineStr"/>
+      <c r="F811" t="inlineStr"/>
+      <c r="G811" t="inlineStr"/>
+      <c r="H811" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -67292,7 +67307,6 @@
         <v/>
       </c>
     </row>
-    <row r="3"/>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
@@ -69385,7 +69399,6 @@
         </is>
       </c>
     </row>
-    <row r="48"/>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>

--- a/data/members.xlsx
+++ b/data/members.xlsx
@@ -5,10 +5,10 @@
   <workbookPr codeName="현재_통합_문서"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ys2ok\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/06c0feee4e58a39d/Desktop/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{41169659-3FDA-40D2-BF22-D08BD8794E27}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="1" documentId="13_ncr:1_{41169659-3FDA-40D2-BF22-D08BD8794E27}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{25DFB2DA-748D-4F1C-87FC-CB8B8C18B9CA}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -8117,7 +8117,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:W809"/>
-  <sheetFormatPr defaultRowHeight="19.2" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultColWidth="12.6328125" defaultRowHeight="19.2" x14ac:dyDescent="0.45"/>
   <sheetData>
     <row r="1" spans="1:23" x14ac:dyDescent="0.45">
       <c r="A1" t="s">
@@ -35226,7 +35226,7 @@
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError sqref="A1:W811" numberStoredAsText="1"/>
+    <ignoredError sqref="A1:W212 A214:W811 A213:B213 D213:W213" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/members.xlsx
+++ b/data/members.xlsx
@@ -2953,7 +2953,7 @@
         <v>킹</v>
       </c>
       <c r="H68" t="str">
-        <v>캄몬스타즈</v>
+        <v>FA</v>
       </c>
     </row>
     <row r="69">

--- a/data/members.xlsx
+++ b/data/members.xlsx
@@ -3286,7 +3286,7 @@
         <v>4</v>
       </c>
       <c r="H77" t="str">
-        <v>캄몬스타즈</v>
+        <v>FA</v>
       </c>
       <c r="K77" t="str">
         <v>거성대, 케이대, 츠캄몬스타즈, 캄몬스타즈</v>
@@ -3389,7 +3389,7 @@
         <v>5</v>
       </c>
       <c r="H79" t="str">
-        <v>캄몬스타즈</v>
+        <v>FA</v>
       </c>
       <c r="K79" t="str">
         <v>복덕방, 츠캄몬스타즈, 캄몬스타즈</v>
